--- a/data/trans_orig/P79A1_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P79A1_2023-Clase-trans_orig.xlsx
@@ -725,27 +725,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>4015</t>
+          <t>4575</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>922</t>
+          <t>1115</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5187</t>
+          <t>5763</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>77,4%</t>
+          <t>79,39%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3694</t>
+          <t>4063</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -795,27 +795,27 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>7709</t>
+          <t>8638</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4370</t>
+          <t>4251</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8881</t>
+          <t>9826</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>49,2%</t>
+          <t>43,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1172</t>
+          <t>1188</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -848,12 +848,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4267</t>
+          <t>4648</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,26%</t>
+          <t>80,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1172</t>
+          <t>1188</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -918,12 +918,12 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4511</t>
+          <t>5575</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>50,8%</t>
+          <t>56,74%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5187</t>
+          <t>5763</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5187</t>
+          <t>5763</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5187</t>
+          <t>5763</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3694</t>
+          <t>4063</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3694</t>
+          <t>4063</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3694</t>
+          <t>4063</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>8881</t>
+          <t>9826</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>8881</t>
+          <t>9826</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>8881</t>
+          <t>9826</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,27 +1068,27 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6870</t>
+          <t>7595</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3303</t>
+          <t>2513</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8298</t>
+          <t>9172</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>82,79%</t>
+          <t>82,81%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1103,27 +1103,27 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3473</t>
+          <t>3820</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1386</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4105</t>
+          <t>4467</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>84,61%</t>
+          <t>85,52%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>35,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1138,27 +1138,27 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>10343</t>
+          <t>11415</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6618</t>
+          <t>6958</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12403</t>
+          <t>13639</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>83,39%</t>
+          <t>83,69%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>53,36%</t>
+          <t>51,02%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1428</t>
+          <t>1577</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1191,12 +1191,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4995</t>
+          <t>6659</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>60,2%</t>
+          <t>72,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>647</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1226,12 +1226,12 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2719</t>
+          <t>2863</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>66,24%</t>
+          <t>64,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2060</t>
+          <t>2224</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
@@ -1261,12 +1261,12 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5785</t>
+          <t>6681</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>46,64%</t>
+          <t>48,98%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8298</t>
+          <t>9172</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8298</t>
+          <t>9172</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8298</t>
+          <t>9172</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4105</t>
+          <t>4467</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4105</t>
+          <t>4467</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4105</t>
+          <t>4467</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>12403</t>
+          <t>13639</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>12403</t>
+          <t>13639</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>12403</t>
+          <t>13639</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>5047</t>
+          <t>5494</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>5047</t>
+          <t>5494</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5047</t>
+          <t>5494</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5047</t>
+          <t>5494</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5047</t>
+          <t>5494</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>5047</t>
+          <t>5494</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>5047</t>
+          <t>5494</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>5047</t>
+          <t>5494</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,27 +1754,27 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8795</t>
+          <t>9321</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5931</t>
+          <t>5756</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9603</t>
+          <t>10337</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>61,76%</t>
+          <t>55,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1789,27 +1789,27 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5958</t>
+          <t>6950</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3645</t>
+          <t>4561</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6564</t>
+          <t>7635</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>55,53%</t>
+          <t>59,73%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1824,27 +1824,27 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>14753</t>
+          <t>16270</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11358</t>
+          <t>12822</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16167</t>
+          <t>17972</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>70,26%</t>
+          <t>71,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>808</t>
+          <t>1016</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1877,12 +1877,12 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3672</t>
+          <t>4581</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1892,7 +1892,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>44,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>685</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1912,12 +1912,12 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2919</t>
+          <t>3074</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>44,47%</t>
+          <t>40,27%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1414</t>
+          <t>1702</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
@@ -1947,12 +1947,12 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4809</t>
+          <t>5150</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>28,66%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9603</t>
+          <t>10337</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9603</t>
+          <t>10337</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9603</t>
+          <t>10337</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6564</t>
+          <t>7635</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6564</t>
+          <t>7635</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6564</t>
+          <t>7635</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>16167</t>
+          <t>17972</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>16167</t>
+          <t>17972</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>16167</t>
+          <t>17972</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2490</t>
+          <t>2186</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -2132,27 +2132,27 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>5896</t>
+          <t>6398</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3367</t>
+          <t>3747</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7300</t>
+          <t>7961</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>80,77%</t>
+          <t>80,37%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>46,13%</t>
+          <t>47,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2167,27 +2167,27 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>8386</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5707</t>
+          <t>5565</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9790</t>
+          <t>10146</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>85,66%</t>
+          <t>84,6%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>58,3%</t>
+          <t>54,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2245,7 +2245,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1404</t>
+          <t>1563</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2255,12 +2255,12 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3933</t>
+          <t>4214</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>53,87%</t>
+          <t>52,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,7 +2280,7 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1404</t>
+          <t>1563</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
@@ -2290,12 +2290,12 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4083</t>
+          <t>4581</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
@@ -2305,7 +2305,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>41,7%</t>
+          <t>45,15%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2490</t>
+          <t>2186</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2490</t>
+          <t>2186</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2490</t>
+          <t>2186</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>7300</t>
+          <t>7961</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>7300</t>
+          <t>7961</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7300</t>
+          <t>7961</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>9790</t>
+          <t>10146</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>9790</t>
+          <t>10146</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>9790</t>
+          <t>10146</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2425,7 +2425,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>1790</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1251</t>
+          <t>1373</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1412</t>
+          <t>3163</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>1790</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>1790</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>1790</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1251</t>
+          <t>1373</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1251</t>
+          <t>1373</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1251</t>
+          <t>1373</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1412</t>
+          <t>3163</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1412</t>
+          <t>3163</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1412</t>
+          <t>3163</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>27378</t>
+          <t>30961</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>22062</t>
+          <t>24631</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>29989</t>
+          <t>33683</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>70,9%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>20272</t>
+          <t>22604</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>16686</t>
+          <t>18895</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>22292</t>
+          <t>24805</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>88,47%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>72,82%</t>
+          <t>74,1%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>47651</t>
+          <t>53565</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>41420</t>
+          <t>46813</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>50988</t>
+          <t>57330</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>88,73%</t>
+          <t>88,92%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>77,13%</t>
+          <t>77,71%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>95,17%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3409</t>
+          <t>3781</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>798</t>
+          <t>1059</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>8725</t>
+          <t>10111</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>2641</t>
+          <t>2895</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>694</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>6227</t>
+          <t>6604</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>6050</t>
+          <t>6676</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2713</t>
+          <t>2911</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>12281</t>
+          <t>13428</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>22,29%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>30787</t>
+          <t>34742</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>30787</t>
+          <t>34742</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>30787</t>
+          <t>34742</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>22913</t>
+          <t>25499</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>22913</t>
+          <t>25499</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>22913</t>
+          <t>25499</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>53701</t>
+          <t>60241</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>53701</t>
+          <t>60241</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>53701</t>
+          <t>60241</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
